--- a/backend/safety/scenario.xlsx
+++ b/backend/safety/scenario.xlsx
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">

--- a/backend/safety/scenario.xlsx
+++ b/backend/safety/scenario.xlsx
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">

--- a/backend/safety/scenario.xlsx
+++ b/backend/safety/scenario.xlsx
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
